--- a/Regelsæt.xlsx
+++ b/Regelsæt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\RPA\Leverancer\Tilføjelse af medarbejders primære organisation til borgere\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED2116A-B828-4D86-8024-50C3E40959EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83DAD0DC-AD5B-45B2-A052-866EBCF58E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2040" yWindow="1308" windowWidth="17280" windowHeight="8880" xr2:uid="{36CB9CF9-9FEC-4F77-BCC8-BA6B4F3B8E1C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{36CB9CF9-9FEC-4F77-BCC8-BA6B4F3B8E1C}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -36,48 +36,60 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Organisationer</t>
   </si>
   <si>
-    <t>CFU Familierådgivningen</t>
-  </si>
-  <si>
-    <t>CFU Familierådgivningen - Rådgivere</t>
-  </si>
-  <si>
-    <t>Ungerådgivningen - Særlig funktion</t>
-  </si>
-  <si>
-    <t>Ungerådgivningen Social 1 - Rådgivere Børn</t>
-  </si>
-  <si>
-    <t>Ungerådgivningen Social 1 - Rådgivere Voksne</t>
-  </si>
-  <si>
     <t>Ungerådgivningen Social 1 - Vagt &amp; Visitation</t>
   </si>
   <si>
-    <t>Ungerådgivningen Social 2 - Rådgivere Børn</t>
-  </si>
-  <si>
-    <t>Ungerådgivningen Social 2 - Rådgivere Voksne</t>
-  </si>
-  <si>
     <t>Ungerådgivningen Special - Kompensation</t>
   </si>
   <si>
-    <t>Ungerådgivningen Special - Rådgivere Børn</t>
-  </si>
-  <si>
-    <t>Ungerådgivningen Special - Rådgivere Voksne</t>
-  </si>
-  <si>
-    <t>Ungerådgivningen Ungeindsats - Rådgivere Børn</t>
-  </si>
-  <si>
-    <t>Ungerådgivningen Ungeindsats - Rådgivere Voksne</t>
+    <t>Social og jobrådgivningen</t>
+  </si>
+  <si>
+    <t>Specialenheden</t>
+  </si>
+  <si>
+    <t>Voksenrådgivningen</t>
+  </si>
+  <si>
+    <t>Ungerådgivningen 1</t>
+  </si>
+  <si>
+    <t>Ungerådgivningen 2</t>
+  </si>
+  <si>
+    <t>Ungerådgivningen 3</t>
+  </si>
+  <si>
+    <t>Familierådgivningen</t>
+  </si>
+  <si>
+    <t>Voksenrådgivningen § 100</t>
+  </si>
+  <si>
+    <t>Kriminalpræventive Indsatser</t>
+  </si>
+  <si>
+    <t>Ungeindsatser 1</t>
+  </si>
+  <si>
+    <t>Ungeindsatser 2</t>
+  </si>
+  <si>
+    <t>Ungeindsatser 3</t>
+  </si>
+  <si>
+    <t>Social og udvikling</t>
+  </si>
+  <si>
+    <t>Bostøtte Voksne</t>
+  </si>
+  <si>
+    <t>Social og jobindsatser</t>
   </si>
 </sst>
 </file>
@@ -461,80 +473,100 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B6B13AE-FF90-4899-8C61-8E4F54D18798}">
-  <dimension ref="A1:A14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:A18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="41.44140625" customWidth="1"/>
+    <col min="1" max="1" width="41.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
